--- a/02-Execucao/01-Questionario/04-Resultados_iGovTI/20260621-iGovTI-2026.xlsx
+++ b/02-Execucao/01-Questionario/04-Resultados_iGovTI/20260621-iGovTI-2026.xlsx
@@ -787,7 +787,7 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0.02520176788858586</v>
+        <v>0.01930982091272491</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -814,13 +814,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K2">
-        <v>0.146851692761069</v>
+        <v>0.1365707428874915</v>
       </c>
       <c r="L2">
-        <v>0.1358076160914104</v>
+        <v>0.07639178405141839</v>
       </c>
       <c r="M2">
-        <v>0.04825117618651868</v>
+        <v>0.03697048457509202</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -828,16 +828,16 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.1748512725327376</v>
+        <v>0.08796744894095609</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3">
-        <v>0.2231537805772504</v>
+        <v>0.1431217320578831</v>
       </c>
       <c r="E3">
-        <v>0.2069515675311097</v>
+        <v>0.02488774919502245</v>
       </c>
       <c r="F3">
         <v>0.03780059893625475</v>
@@ -849,19 +849,19 @@
         <v>0.05</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.4916666666666666</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.3731462782578582</v>
+        <v>0.0150523783172804</v>
       </c>
       <c r="L3">
         <v>0.04999999999999995</v>
       </c>
       <c r="M3">
-        <v>0.1306740451789215</v>
+        <v>0.0375236230727873</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -910,16 +910,16 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.2212173458914763</v>
+        <v>0.1533646449096753</v>
       </c>
       <c r="C5" t="s">
         <v>128</v>
       </c>
       <c r="D5">
-        <v>0.1151533229169725</v>
+        <v>0.04911057522779355</v>
       </c>
       <c r="E5">
-        <v>0.5105821077103836</v>
+        <v>0.341345413184231</v>
       </c>
       <c r="F5">
         <v>0.4146258265874885</v>
@@ -928,7 +928,7 @@
         <v>0.2021476696413982</v>
       </c>
       <c r="H5">
-        <v>0.3042330666261704</v>
+        <v>0.2571146385352526</v>
       </c>
       <c r="I5">
         <v>0.5</v>
@@ -937,13 +937,13 @@
         <v>0.0833333333333335</v>
       </c>
       <c r="K5">
-        <v>0.2295952006974917</v>
+        <v>0.03131973884992489</v>
       </c>
       <c r="L5">
         <v>0.2546392801713945</v>
       </c>
       <c r="M5">
-        <v>0.3182229600241221</v>
+        <v>0.2487148849976801</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -951,19 +951,19 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>0.1914343366033805</v>
+        <v>0.09191315598661183</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6">
-        <v>0.1540407644136793</v>
+        <v>0.01216576931116455</v>
       </c>
       <c r="E6">
-        <v>0.4884733890523054</v>
+        <v>0.3192366945261526</v>
       </c>
       <c r="F6">
-        <v>0.2259420820693767</v>
+        <v>0.03787717275399195</v>
       </c>
       <c r="G6">
         <v>0.2994134949523378</v>
@@ -984,7 +984,7 @@
         <v>0.2358762519400116</v>
       </c>
       <c r="M6">
-        <v>0.2256343068962985</v>
+        <v>0.1648497088626512</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -992,7 +992,7 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>0.2645959319888789</v>
+        <v>0.2411373679833352</v>
       </c>
       <c r="C7" t="s">
         <v>128</v>
@@ -1001,10 +1001,10 @@
         <v>0.1216576931116455</v>
       </c>
       <c r="E7">
-        <v>0.497754983900449</v>
+        <v>0.3285182893742963</v>
       </c>
       <c r="F7">
-        <v>0.2215457707575403</v>
+        <v>0.15</v>
       </c>
       <c r="G7">
         <v>0.4032683763560195</v>
@@ -1013,19 +1013,19 @@
         <v>0.9400037895556652</v>
       </c>
       <c r="I7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.6333333333333333</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="K7">
-        <v>0.2864973503777228</v>
+        <v>0.2551776115277979</v>
       </c>
       <c r="L7">
         <v>0.0736082159485815</v>
       </c>
       <c r="M7">
-        <v>0.3953265158048255</v>
+        <v>0.3504128688766328</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1074,7 +1074,7 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>0.3219920493521544</v>
+        <v>0.2557711225891841</v>
       </c>
       <c r="C9" t="s">
         <v>128</v>
@@ -1083,10 +1083,10 @@
         <v>0.2058959357818603</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0.6173091736315381</v>
       </c>
       <c r="F9">
-        <v>0.2987024864354205</v>
+        <v>0.1106375771200357</v>
       </c>
       <c r="G9">
         <v>0.15</v>
@@ -1095,19 +1095,19 @@
         <v>0.7320091407607904</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J9">
-        <v>0.291666666666667</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="K9">
-        <v>0.3060530547806477</v>
+        <v>0.1234564820766533</v>
       </c>
       <c r="L9">
         <v>0.1499999999999999</v>
       </c>
       <c r="M9">
-        <v>0.4281729623466295</v>
+        <v>0.3013867139135666</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1115,7 +1115,7 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>0.07347034058440753</v>
+        <v>0.06955825063336939</v>
       </c>
       <c r="C10" t="s">
         <v>127</v>
@@ -1142,13 +1142,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K10">
-        <v>0.2022897775864878</v>
+        <v>0.1611659780921776</v>
       </c>
       <c r="L10">
         <v>0.1165463419185874</v>
       </c>
       <c r="M10">
-        <v>0.1406659391394269</v>
+        <v>0.1331758716838599</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1156,22 +1156,22 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>0.3764449182692471</v>
+        <v>0.2182328048103805</v>
       </c>
       <c r="C11" t="s">
         <v>128</v>
       </c>
       <c r="D11">
-        <v>0.5471590975134757</v>
+        <v>0.3024676777542963</v>
       </c>
       <c r="E11">
-        <v>0.3242142443651571</v>
+        <v>0.15</v>
       </c>
       <c r="F11">
         <v>0.1256011978725095</v>
       </c>
       <c r="G11">
-        <v>0.3634700691411702</v>
+        <v>0.09977174843737169</v>
       </c>
       <c r="H11">
         <v>0.15</v>
@@ -1183,13 +1183,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K11">
-        <v>0.2228516773336428</v>
+        <v>0.1714469279657551</v>
       </c>
       <c r="L11">
         <v>0.1499999999999999</v>
       </c>
       <c r="M11">
-        <v>0.2203106011434691</v>
+        <v>0.1411920198943285</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>23</v>
       </c>
       <c r="B12">
-        <v>0.2089287427258555</v>
+        <v>0.1973663299796736</v>
       </c>
       <c r="C12" t="s">
         <v>128</v>
@@ -1209,7 +1209,7 @@
         <v>0.7240362395526927</v>
       </c>
       <c r="F12">
-        <v>0.2329559272334677</v>
+        <v>0.1134017968087642</v>
       </c>
       <c r="G12">
         <v>0.15</v>
@@ -1230,7 +1230,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M12">
-        <v>0.2927688577405731</v>
+        <v>0.2706315213035547</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>24</v>
       </c>
       <c r="B13">
-        <v>0.1072162950405251</v>
+        <v>0.09806953436809951</v>
       </c>
       <c r="C13" t="s">
         <v>127</v>
@@ -1250,7 +1250,7 @@
         <v>0.2887908842572418</v>
       </c>
       <c r="F13">
-        <v>0.1880649093153848</v>
+        <v>0.1137136660976745</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.1204339842333369</v>
+        <v>0.09987208448618179</v>
       </c>
       <c r="L13">
         <v>0.3217525038800234</v>
       </c>
       <c r="M13">
-        <v>0.1603594898485178</v>
+        <v>0.1428471485440407</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1279,7 +1279,7 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>0.4866950952963253</v>
+        <v>0.4593295924233849</v>
       </c>
       <c r="C14" t="s">
         <v>129</v>
@@ -1288,10 +1288,10 @@
         <v>0.4782527941035971</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0.8086545868157691</v>
       </c>
       <c r="F14">
-        <v>0.4183714244622249</v>
+        <v>0.2939375336120233</v>
       </c>
       <c r="G14">
         <v>0.7688378701590762</v>
@@ -1312,7 +1312,7 @@
         <v>0.3217525038800234</v>
       </c>
       <c r="M14">
-        <v>0.4944163808833356</v>
+        <v>0.4420225287380281</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1320,7 +1320,7 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>0.1116328442728372</v>
+        <v>0.09919798692846593</v>
       </c>
       <c r="C15" t="s">
         <v>127</v>
@@ -1347,13 +1347,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K15">
-        <v>0.192746920699082</v>
+        <v>0.06203198659216763</v>
       </c>
       <c r="L15">
         <v>0.0736082159485815</v>
       </c>
       <c r="M15">
-        <v>0.09761441293189892</v>
+        <v>0.0738066985195609</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1361,13 +1361,13 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>0.06570874611014509</v>
+        <v>0.02433201012873679</v>
       </c>
       <c r="C16" t="s">
         <v>127</v>
       </c>
       <c r="D16">
-        <v>0.08969132509797501</v>
+        <v>0.0301543374510125</v>
       </c>
       <c r="E16">
         <v>0.02511225080497755</v>
@@ -1385,16 +1385,16 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0.2416666666666666</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>0.1521401559893879</v>
+        <v>0.0161557783727647</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.04377440175891893</v>
+        <v>0.01900693927304798</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1443,19 +1443,19 @@
         <v>29</v>
       </c>
       <c r="B18">
-        <v>0.193751396047198</v>
+        <v>0.12720036041123</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D18">
-        <v>0.1782471241195326</v>
+        <v>0.08730768929385523</v>
       </c>
       <c r="E18">
         <v>0.3634541318423091</v>
       </c>
       <c r="F18">
-        <v>0.09303978756044337</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0.2572712654381399</v>
@@ -1470,13 +1470,13 @@
         <v>0.2083333333333334</v>
       </c>
       <c r="K18">
-        <v>0.226638766729288</v>
+        <v>0.07829934712481212</v>
       </c>
       <c r="L18">
         <v>0.3264261019757188</v>
       </c>
       <c r="M18">
-        <v>0.2079315240288065</v>
+        <v>0.1636859938296688</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1484,16 +1484,16 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>0.3414084811168441</v>
+        <v>0.2120587416021165</v>
       </c>
       <c r="C19" t="s">
         <v>128</v>
       </c>
       <c r="D19">
-        <v>0.4759849833588806</v>
+        <v>0.2588846884513499</v>
       </c>
       <c r="E19">
-        <v>0.8086545868157691</v>
+        <v>0.7240362395526927</v>
       </c>
       <c r="F19">
         <v>0.0772395956339562</v>
@@ -1511,13 +1511,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K19">
-        <v>0.2904122050742952</v>
+        <v>0.09213674322672843</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0.2183254989547372</v>
+        <v>0.169231969582122</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1525,7 +1525,7 @@
         <v>31</v>
       </c>
       <c r="B20">
-        <v>0.1667612808938213</v>
+        <v>0.1503689673242781</v>
       </c>
       <c r="C20" t="s">
         <v>128</v>
@@ -1546,19 +1546,19 @@
         <v>0.06929180601605563</v>
       </c>
       <c r="I20">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.3250000000000001</v>
+        <v>0.2416666666666666</v>
       </c>
       <c r="K20">
-        <v>0.3961055406311757</v>
+        <v>0.2237899178007589</v>
       </c>
       <c r="L20">
         <v>0.1499999999999999</v>
       </c>
       <c r="M20">
-        <v>0.1820910628609429</v>
+        <v>0.1507064229561005</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1566,7 +1566,7 @@
         <v>32</v>
       </c>
       <c r="B21">
-        <v>0.2114956586214317</v>
+        <v>0.1933073777410211</v>
       </c>
       <c r="C21" t="s">
         <v>128</v>
@@ -1578,7 +1578,7 @@
         <v>0.05</v>
       </c>
       <c r="F21">
-        <v>0.5036216264259995</v>
+        <v>0.3155567171106147</v>
       </c>
       <c r="G21">
         <v>0.15</v>
@@ -1599,7 +1599,7 @@
         <v>0.5828867762913704</v>
       </c>
       <c r="M21">
-        <v>0.2778296020138071</v>
+        <v>0.2430064122609939</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1607,7 +1607,7 @@
         <v>33</v>
       </c>
       <c r="B22">
-        <v>0.3441780533427977</v>
+        <v>0.1961299974886796</v>
       </c>
       <c r="C22" t="s">
         <v>128</v>
@@ -1616,31 +1616,31 @@
         <v>0.2114695354218515</v>
       </c>
       <c r="E22">
-        <v>0.3424214244365157</v>
+        <v>0.07533675241493265</v>
       </c>
       <c r="F22">
-        <v>0.5217363026809185</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>0.5772821456925405</v>
+        <v>0.313583824988742</v>
       </c>
       <c r="H22">
-        <v>0.5312864872175717</v>
+        <v>0.2570609997027318</v>
       </c>
       <c r="I22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>0.7749999999999999</v>
+        <v>0.4083333333333332</v>
       </c>
       <c r="K22">
-        <v>0.5519503888368642</v>
+        <v>0.3687403719499631</v>
       </c>
       <c r="L22">
-        <v>0.2391237480599879</v>
+        <v>0.0736082159485815</v>
       </c>
       <c r="M22">
-        <v>0.465552586577778</v>
+        <v>0.1821005343777428</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1648,19 +1648,19 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.2347837195395864</v>
+        <v>0.1865404394078243</v>
       </c>
       <c r="C23" t="s">
         <v>128</v>
       </c>
       <c r="D23">
-        <v>0.2534218830150621</v>
+        <v>0.1879471909000925</v>
       </c>
       <c r="E23">
-        <v>0.1346183472630763</v>
+        <v>0.02511225080497755</v>
       </c>
       <c r="F23">
-        <v>0.2797236988299656</v>
+        <v>0.1950160465279212</v>
       </c>
       <c r="G23">
         <v>0.1179431620808941</v>
@@ -1681,7 +1681,7 @@
         <v>0.1797079160199959</v>
       </c>
       <c r="M23">
-        <v>0.217737350341637</v>
+        <v>0.1852538316721145</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1689,7 +1689,7 @@
         <v>35</v>
       </c>
       <c r="B24">
-        <v>0.06933708829051677</v>
+        <v>0.06375366609313773</v>
       </c>
       <c r="C24" t="s">
         <v>127</v>
@@ -1698,7 +1698,7 @@
         <v>0.0301543374510125</v>
       </c>
       <c r="E24">
-        <v>0.3242142443651571</v>
+        <v>0.2545285466190942</v>
       </c>
       <c r="F24">
         <v>0.0772395956339562</v>
@@ -1722,7 +1722,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M24">
-        <v>0.1051734322457734</v>
+        <v>0.09448344060072406</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1730,7 +1730,7 @@
         <v>36</v>
       </c>
       <c r="B25">
-        <v>0.1446526061467258</v>
+        <v>0.1163332764623794</v>
       </c>
       <c r="C25" t="s">
         <v>127</v>
@@ -1742,7 +1742,7 @@
         <v>0.07533675241493265</v>
       </c>
       <c r="F25">
-        <v>0.3308445815415552</v>
+        <v>0.07552462405477231</v>
       </c>
       <c r="G25">
         <v>0.1127853144532854</v>
@@ -1757,13 +1757,13 @@
         <v>0.4083333333333332</v>
       </c>
       <c r="K25">
-        <v>0.354180055623464</v>
+        <v>0.3160570478394817</v>
       </c>
       <c r="L25">
         <v>0.2546392801713945</v>
       </c>
       <c r="M25">
-        <v>0.2769511415183663</v>
+        <v>0.2227310974276348</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1771,13 +1771,13 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>0.5077238904760649</v>
+        <v>0.4338685236850021</v>
       </c>
       <c r="C26" t="s">
         <v>129</v>
       </c>
       <c r="D26">
-        <v>0.6125191394125646</v>
+        <v>0.457911772954696</v>
       </c>
       <c r="E26">
         <v>0.4480724791053855</v>
@@ -1853,19 +1853,19 @@
         <v>39</v>
       </c>
       <c r="B28">
-        <v>0.2986382504269866</v>
+        <v>0.1520723031010568</v>
       </c>
       <c r="C28" t="s">
         <v>128</v>
       </c>
       <c r="D28">
-        <v>0.2158837109968267</v>
+        <v>0.01216576931116455</v>
       </c>
       <c r="E28">
-        <v>0.6814368103037126</v>
+        <v>0.2887908842572418</v>
       </c>
       <c r="F28">
-        <v>0.08759618357188245</v>
+        <v>0.0509979803806467</v>
       </c>
       <c r="G28">
         <v>0.1381276917972278</v>
@@ -1880,13 +1880,13 @@
         <v>0.6916666666666664</v>
       </c>
       <c r="K28">
-        <v>0.6032585137399658</v>
+        <v>0.4534503870106931</v>
       </c>
       <c r="L28">
         <v>0.1603436880742709</v>
       </c>
       <c r="M28">
-        <v>0.3743251298659896</v>
+        <v>0.2800301049159163</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1894,7 +1894,7 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>0.09083003692283034</v>
+        <v>0.05090511610313125</v>
       </c>
       <c r="C29" t="s">
         <v>127</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.59520045497346</v>
+        <v>0.341345413184231</v>
       </c>
       <c r="F29">
-        <v>0.2403872304121631</v>
+        <v>0.03787717275399195</v>
       </c>
       <c r="G29">
         <v>0.05273417468906039</v>
@@ -1927,7 +1927,7 @@
         <v>0.07639178405141835</v>
       </c>
       <c r="M29">
-        <v>0.1739027251566917</v>
+        <v>0.09746267550538897</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1935,7 +1935,7 @@
         <v>41</v>
       </c>
       <c r="B30">
-        <v>0.309235534685493</v>
+        <v>0.2902940949541311</v>
       </c>
       <c r="C30" t="s">
         <v>128</v>
@@ -1944,10 +1944,10 @@
         <v>0.2744907033325922</v>
       </c>
       <c r="E30">
-        <v>0.4212107122182578</v>
+        <v>0.3863678633452264</v>
       </c>
       <c r="F30">
-        <v>0.2260435456907571</v>
+        <v>0.1818535108110998</v>
       </c>
       <c r="G30">
         <v>0.2817691859871062</v>
@@ -1962,13 +1962,13 @@
         <v>0.3250000000000001</v>
       </c>
       <c r="K30">
-        <v>0.385410863922645</v>
+        <v>0.2605707583149178</v>
       </c>
       <c r="L30">
         <v>0.2226460419900018</v>
       </c>
       <c r="M30">
-        <v>0.341012980126475</v>
+        <v>0.3047477962812494</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1976,7 +1976,7 @@
         <v>42</v>
       </c>
       <c r="B31">
-        <v>0.2506674692863792</v>
+        <v>0.1705648961967423</v>
       </c>
       <c r="C31" t="s">
         <v>128</v>
@@ -1985,13 +1985,13 @@
         <v>0.03649730793349365</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0.7240362395526927</v>
       </c>
       <c r="F31">
-        <v>0.2757415136099722</v>
+        <v>0.05260718438054437</v>
       </c>
       <c r="G31">
-        <v>0.2100614153134851</v>
+        <v>0.04703757374831129</v>
       </c>
       <c r="H31">
         <v>0.7172894314544931</v>
@@ -2003,13 +2003,13 @@
         <v>0.3250000000000001</v>
       </c>
       <c r="K31">
-        <v>0.2370714443181691</v>
+        <v>0.216509544571014</v>
       </c>
       <c r="L31">
-        <v>0.3249999999999997</v>
+        <v>0.07639178405141839</v>
       </c>
       <c r="M31">
-        <v>0.4465464058784665</v>
+        <v>0.2931824282310064</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -2017,7 +2017,7 @@
         <v>43</v>
       </c>
       <c r="B32">
-        <v>0.006554754222307241</v>
+        <v>0.004469150606118573</v>
       </c>
       <c r="C32" t="s">
         <v>127</v>
@@ -2041,16 +2041,16 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0.1833333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="K32">
-        <v>0.06890342546983462</v>
+        <v>0.04697960827488724</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0.01254969898294786</v>
+        <v>0.008556612942918993</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -2181,7 +2181,7 @@
         <v>47</v>
       </c>
       <c r="B36">
-        <v>0.6406585749527975</v>
+        <v>0.6290961622066156</v>
       </c>
       <c r="C36" t="s">
         <v>129</v>
@@ -2193,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0.3760474687485484</v>
+        <v>0.256493338323845</v>
       </c>
       <c r="G36">
         <v>0.843208087505629</v>
@@ -2214,7 +2214,7 @@
         <v>0.5107389802428087</v>
       </c>
       <c r="M36">
-        <v>0.6528227044112944</v>
+        <v>0.630685367974276</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2263,7 +2263,7 @@
         <v>49</v>
       </c>
       <c r="B38">
-        <v>0.03352570493221324</v>
+        <v>0.02537353464276431</v>
       </c>
       <c r="C38" t="s">
         <v>127</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0.1615321781099631</v>
+        <v>0.07723959563395622</v>
       </c>
       <c r="G38">
         <v>0.08349577659101232</v>
@@ -2296,7 +2296,7 @@
         <v>0.07639178405141835</v>
       </c>
       <c r="M38">
-        <v>0.06418814357044023</v>
+        <v>0.04858003993748611</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2345,16 +2345,16 @@
         <v>51</v>
       </c>
       <c r="B40">
-        <v>0.2520929836527444</v>
+        <v>0.2392309071647302</v>
       </c>
       <c r="C40" t="s">
         <v>128</v>
       </c>
       <c r="D40">
-        <v>0.176756601619568</v>
+        <v>0.1640242302642141</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0.9153816527369236</v>
       </c>
       <c r="F40">
         <v>0.2534196702949982</v>
@@ -2378,7 +2378,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M40">
-        <v>0.3209952541937802</v>
+        <v>0.3080145500533631</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2386,19 +2386,19 @@
         <v>52</v>
       </c>
       <c r="B41">
-        <v>0.2447309646600977</v>
+        <v>0.2214650574475474</v>
       </c>
       <c r="C41" t="s">
         <v>128</v>
       </c>
       <c r="D41">
-        <v>0.3142239655134678</v>
+        <v>0.2833024922218941</v>
       </c>
       <c r="E41">
         <v>0.5326908263684618</v>
       </c>
       <c r="F41">
-        <v>0.1900491141997163</v>
+        <v>0.1022134265407505</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>0.1165463419185874</v>
       </c>
       <c r="M41">
-        <v>0.1811730207254033</v>
+        <v>0.1649088551798388</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2427,19 +2427,19 @@
         <v>53</v>
       </c>
       <c r="B42">
-        <v>0.7781496151063866</v>
+        <v>0.7040554378759768</v>
       </c>
       <c r="C42" t="s">
         <v>130</v>
       </c>
       <c r="D42">
-        <v>0.7794294621540654</v>
+        <v>0.717586515570918</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>0.9227491510044961</v>
+        <v>0.5357637215321341</v>
       </c>
       <c r="G42">
         <v>0.351561164593736</v>
@@ -2454,13 +2454,13 @@
         <v>0.9166666666666665</v>
       </c>
       <c r="K42">
-        <v>0.7980866402208973</v>
+        <v>0.723182576856261</v>
       </c>
       <c r="L42">
         <v>0.8957216940728419</v>
       </c>
       <c r="M42">
-        <v>0.7769790735280631</v>
+        <v>0.6916799832697542</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2468,7 +2468,7 @@
         <v>54</v>
       </c>
       <c r="B43">
-        <v>0.8005815495135801</v>
+        <v>0.730627879068066</v>
       </c>
       <c r="C43" t="s">
         <v>130</v>
@@ -2477,10 +2477,10 @@
         <v>0.8653999679978164</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0.9153816527369236</v>
       </c>
       <c r="F43">
-        <v>0.6462514869432154</v>
+        <v>0.3416741996364068</v>
       </c>
       <c r="G43">
         <v>0.5693195218228373</v>
@@ -2489,19 +2489,19 @@
         <v>0.7918176209190417</v>
       </c>
       <c r="I43">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>0.7749999999999999</v>
+        <v>0.6916666666666664</v>
       </c>
       <c r="K43">
-        <v>0.830139894640614</v>
+        <v>0.4757045883353951</v>
       </c>
       <c r="L43">
         <v>0.6265290557486204</v>
       </c>
       <c r="M43">
-        <v>0.7412989547577536</v>
+        <v>0.6073660143195199</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2509,40 +2509,40 @@
         <v>55</v>
       </c>
       <c r="B44">
-        <v>0.3470098692420663</v>
+        <v>0.1712639661960675</v>
       </c>
       <c r="C44" t="s">
         <v>128</v>
       </c>
       <c r="D44">
-        <v>0.2250517404111412</v>
+        <v>0.1468446769408177</v>
       </c>
       <c r="E44">
-        <v>0.4510760112522847</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0.6354744242121289</v>
+        <v>0.1487853663914966</v>
       </c>
       <c r="G44">
-        <v>0.2158845929935531</v>
+        <v>0.1029624262516887</v>
       </c>
       <c r="H44">
         <v>0.3575056703716769</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J44">
-        <v>0.8583333333333334</v>
+        <v>0.0833333333333335</v>
       </c>
       <c r="K44">
-        <v>0.6207408564879744</v>
+        <v>0.2046271795759462</v>
       </c>
       <c r="L44">
-        <v>0.423109970007141</v>
+        <v>0.3509621739585792</v>
       </c>
       <c r="M44">
-        <v>0.4585521514781091</v>
+        <v>0.1935977235291988</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2550,13 +2550,13 @@
         <v>56</v>
       </c>
       <c r="B45">
-        <v>0.1659839245802623</v>
+        <v>0.1294558965699228</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D45">
-        <v>0.1887130872981291</v>
+        <v>0.1400500100534709</v>
       </c>
       <c r="E45">
         <v>0.341345413184231</v>
@@ -2565,10 +2565,10 @@
         <v>0.03787717275399195</v>
       </c>
       <c r="G45">
-        <v>0.1865847795820199</v>
+        <v>0.1029624262516887</v>
       </c>
       <c r="H45">
-        <v>0.09233505021044504</v>
+        <v>0.01764594424833375</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2583,7 +2583,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M45">
-        <v>0.145195948352946</v>
+        <v>0.1197665744431394</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2591,19 +2591,19 @@
         <v>57</v>
       </c>
       <c r="B46">
-        <v>0.1919665423499598</v>
+        <v>0.1843354844303174</v>
       </c>
       <c r="C46" t="s">
         <v>128</v>
       </c>
       <c r="D46">
-        <v>0.1359707665385134</v>
+        <v>0.1232383951831595</v>
       </c>
       <c r="E46">
-        <v>0.1095060964580988</v>
+        <v>0.24389994211122</v>
       </c>
       <c r="F46">
-        <v>0.1735862451682324</v>
+        <v>0.1199088804877533</v>
       </c>
       <c r="G46">
         <v>0.0502282515626283</v>
@@ -2618,13 +2618,13 @@
         <v>0.3833333333333334</v>
       </c>
       <c r="K46">
-        <v>0.5650268252272709</v>
+        <v>0.4901227618626345</v>
       </c>
       <c r="L46">
         <v>0.04999999999999995</v>
       </c>
       <c r="M46">
-        <v>0.2431799931421202</v>
+        <v>0.2402145704570875</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2632,19 +2632,19 @@
         <v>58</v>
       </c>
       <c r="B47">
-        <v>0.2103134916551513</v>
+        <v>0.1718209095143181</v>
       </c>
       <c r="C47" t="s">
         <v>128</v>
       </c>
       <c r="D47">
-        <v>0.2547191276054441</v>
+        <v>0.2292543848947363</v>
       </c>
       <c r="E47">
-        <v>0.3863678633452264</v>
+        <v>0.1791917942041616</v>
       </c>
       <c r="F47">
-        <v>0.2112304355910555</v>
+        <v>0.1106375771200357</v>
       </c>
       <c r="G47">
         <v>0.15</v>
@@ -2665,7 +2665,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M47">
-        <v>0.16970032363168</v>
+        <v>0.1192925460334332</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2673,16 +2673,16 @@
         <v>59</v>
       </c>
       <c r="B48">
-        <v>0.1659104550204143</v>
+        <v>0.1132029216780569</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D48">
         <v>0.08959694710469522</v>
       </c>
       <c r="E48">
-        <v>0.5763662668697268</v>
+        <v>0.1632296302323541</v>
       </c>
       <c r="F48">
         <v>0.1138377988251919</v>
@@ -2694,19 +2694,19 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J48">
-        <v>0.8583333333333334</v>
+        <v>0.7749999999999999</v>
       </c>
       <c r="K48">
-        <v>0.6457088776095199</v>
+        <v>0.4396129909087768</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48">
-        <v>0.2357063999070268</v>
+        <v>0.1347928255537475</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2714,7 +2714,7 @@
         <v>60</v>
       </c>
       <c r="B49">
-        <v>0.08327285797182167</v>
+        <v>0.07470472430435478</v>
       </c>
       <c r="C49" t="s">
         <v>127</v>
@@ -2735,19 +2735,19 @@
         <v>0.05</v>
       </c>
       <c r="I49">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>0.2666666666666668</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="K49">
-        <v>0.2216896923002995</v>
+        <v>0.1316216684585029</v>
       </c>
       <c r="L49">
         <v>0.2655841679600076</v>
       </c>
       <c r="M49">
-        <v>0.1333349445525661</v>
+        <v>0.1169304395588576</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2755,13 +2755,13 @@
         <v>61</v>
       </c>
       <c r="B50">
-        <v>0.1939421590657127</v>
+        <v>0.1576795157441079</v>
       </c>
       <c r="C50" t="s">
         <v>128</v>
       </c>
       <c r="D50">
-        <v>0.2619063667562207</v>
+        <v>0.2109768813348052</v>
       </c>
       <c r="E50">
         <v>0.1002245016099551</v>
@@ -2785,10 +2785,10 @@
         <v>0.09544694339318133</v>
       </c>
       <c r="L50">
-        <v>0.409381514115691</v>
+        <v>0.2650859220185675</v>
       </c>
       <c r="M50">
-        <v>0.1317824415558341</v>
+        <v>0.1089340171689637</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2796,25 +2796,25 @@
         <v>62</v>
       </c>
       <c r="B51">
-        <v>0.5195898042865734</v>
+        <v>0.4514405300182375</v>
       </c>
       <c r="C51" t="s">
         <v>129</v>
       </c>
       <c r="D51">
-        <v>0.5702513396632428</v>
+        <v>0.5459198010409138</v>
       </c>
       <c r="E51">
         <v>0.8932729340788453</v>
       </c>
       <c r="F51">
-        <v>0.4534587792127327</v>
+        <v>0.1938480991398076</v>
       </c>
       <c r="G51">
         <v>0.05</v>
       </c>
       <c r="H51">
-        <v>0.8328891510204127</v>
+        <v>0.6444154386567413</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2823,13 +2823,13 @@
         <v>0.04166666666666666</v>
       </c>
       <c r="K51">
-        <v>0.2472160543045274</v>
+        <v>0.1576882971526574</v>
       </c>
       <c r="L51">
-        <v>0.4273539580099975</v>
+        <v>0.3382302099500095</v>
       </c>
       <c r="M51">
-        <v>0.4732550225736648</v>
+        <v>0.3650302708999074</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2837,13 +2837,13 @@
         <v>63</v>
       </c>
       <c r="B52">
-        <v>0.173647096589045</v>
+        <v>0.1614826832352229</v>
       </c>
       <c r="C52" t="s">
         <v>128</v>
       </c>
       <c r="D52">
-        <v>0.1651574343525928</v>
+        <v>0.139692691641885</v>
       </c>
       <c r="E52">
         <v>0.07533675241493264</v>
@@ -2878,22 +2878,22 @@
         <v>64</v>
       </c>
       <c r="B53">
-        <v>0.221050935522498</v>
+        <v>0.1254274952750478</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D53">
-        <v>0.1885544324776476</v>
+        <v>0.09761499765197017</v>
       </c>
       <c r="E53">
         <v>0.3333178344008364</v>
       </c>
       <c r="F53">
-        <v>0.1875401160920445</v>
+        <v>0.1373148366825888</v>
       </c>
       <c r="G53">
-        <v>0.246646194895505</v>
+        <v>0</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -2902,16 +2902,16 @@
         <v>0.5</v>
       </c>
       <c r="J53">
-        <v>0.2666666666666668</v>
+        <v>0.2083333333333335</v>
       </c>
       <c r="K53">
-        <v>0.4134230889707885</v>
+        <v>0.3415632295327502</v>
       </c>
       <c r="L53">
-        <v>0.3117697900499898</v>
+        <v>0.07639178405141839</v>
       </c>
       <c r="M53">
-        <v>0.250772071366901</v>
+        <v>0.1508646636647283</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2960,40 +2960,40 @@
         <v>66</v>
       </c>
       <c r="B55">
-        <v>0.4729067487998457</v>
+        <v>0.3556247825995705</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D55">
-        <v>0.3641194130330361</v>
+        <v>0.3032905664772133</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55">
-        <v>0.620597730571985</v>
+        <v>0.1553157624419259</v>
       </c>
       <c r="G55">
-        <v>0.3067076102089901</v>
+        <v>0.2759460083070382</v>
       </c>
       <c r="H55">
-        <v>0.5912826976619063</v>
+        <v>0.4499274133891529</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J55">
-        <v>0.4083333333333336</v>
+        <v>0.2666666666666668</v>
       </c>
       <c r="K55">
-        <v>0.3893022716971184</v>
+        <v>0.2730944416681872</v>
       </c>
       <c r="L55">
-        <v>0.5674055621042645</v>
+        <v>0.3509621739585792</v>
       </c>
       <c r="M55">
-        <v>0.5724030909143676</v>
+        <v>0.4034893895862416</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -3001,16 +3001,16 @@
         <v>67</v>
       </c>
       <c r="B56">
-        <v>0.1805142163954287</v>
+        <v>0.1467332094217962</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D56">
         <v>0.1216576931116455</v>
       </c>
       <c r="E56">
-        <v>0.6798188022365362</v>
+        <v>0.3192366945261527</v>
       </c>
       <c r="F56">
         <v>0.01312080762665475</v>
@@ -3028,13 +3028,13 @@
         <v>0.5499999999999998</v>
       </c>
       <c r="K56">
-        <v>0.3065823608956856</v>
+        <v>0.2551776115277979</v>
       </c>
       <c r="L56">
         <v>0.2546392801713945</v>
       </c>
       <c r="M56">
-        <v>0.2343440922264466</v>
+        <v>0.1696671486703959</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -3042,19 +3042,19 @@
         <v>68</v>
       </c>
       <c r="B57">
-        <v>0.330695171391959</v>
+        <v>0.2143910869258308</v>
       </c>
       <c r="C57" t="s">
         <v>128</v>
       </c>
       <c r="D57">
-        <v>0.3076340308442232</v>
+        <v>0.1839481376779283</v>
       </c>
       <c r="E57">
-        <v>0.1632296302323541</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>0.4234482465745323</v>
+        <v>0.1880649093153848</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -3069,13 +3069,13 @@
         <v>0.7749999999999999</v>
       </c>
       <c r="K57">
-        <v>0.564453096516504</v>
+        <v>0.339740906422595</v>
       </c>
       <c r="L57">
         <v>0.07639178405141835</v>
       </c>
       <c r="M57">
-        <v>0.3517867728482807</v>
+        <v>0.2422340529475104</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -3083,7 +3083,7 @@
         <v>69</v>
       </c>
       <c r="B58">
-        <v>0.121724767195325</v>
+        <v>0.09245154448287915</v>
       </c>
       <c r="C58" t="s">
         <v>127</v>
@@ -3092,10 +3092,10 @@
         <v>0.06540252210566475</v>
       </c>
       <c r="E58">
-        <v>0.59520045497346</v>
+        <v>0.4259637604473072</v>
       </c>
       <c r="F58">
-        <v>0.1137136660976745</v>
+        <v>0.03936242287996426</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -3110,13 +3110,13 @@
         <v>0.3250000000000001</v>
       </c>
       <c r="K58">
-        <v>0.2117381161273112</v>
+        <v>0.1221469815147069</v>
       </c>
       <c r="L58">
         <v>0.0736082159485815</v>
       </c>
       <c r="M58">
-        <v>0.173236805123259</v>
+        <v>0.1171904423089602</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -3124,19 +3124,19 @@
         <v>70</v>
       </c>
       <c r="B59">
-        <v>0.2691655025350436</v>
+        <v>0.2228808701329766</v>
       </c>
       <c r="C59" t="s">
         <v>128</v>
       </c>
       <c r="D59">
-        <v>0.3288515688862118</v>
+        <v>0.2670086223030643</v>
       </c>
       <c r="E59">
         <v>0.1441709405186658</v>
       </c>
       <c r="F59">
-        <v>0.1495142377463341</v>
+        <v>0.05007657381773722</v>
       </c>
       <c r="G59">
         <v>0.0971061232038483</v>
@@ -3151,13 +3151,13 @@
         <v>0.7749999999999999</v>
       </c>
       <c r="K59">
-        <v>0.6697004686635449</v>
+        <v>0.5947964052989086</v>
       </c>
       <c r="L59">
         <v>0.02546392801713945</v>
       </c>
       <c r="M59">
-        <v>0.2145769308480283</v>
+        <v>0.1825218531967478</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -3206,16 +3206,16 @@
         <v>72</v>
       </c>
       <c r="B61">
-        <v>0.0947410475738459</v>
+        <v>0.06142740177265096</v>
       </c>
       <c r="C61" t="s">
         <v>127</v>
       </c>
       <c r="D61">
-        <v>0.0577226288678418</v>
+        <v>0.01637019174259785</v>
       </c>
       <c r="E61">
-        <v>0.4259637604473072</v>
+        <v>0.2567270659211546</v>
       </c>
       <c r="F61">
         <v>0.03936242287996428</v>
@@ -3239,7 +3239,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M61">
-        <v>0.1285979044051069</v>
+        <v>0.1026364961242728</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -3247,7 +3247,7 @@
         <v>73</v>
       </c>
       <c r="B62">
-        <v>0.08434771617763075</v>
+        <v>0.05866178214558653</v>
       </c>
       <c r="C62" t="s">
         <v>127</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.4259637604473072</v>
+        <v>0.2567270659211546</v>
       </c>
       <c r="F62">
-        <v>0.2608253136814286</v>
+        <v>0.1864740704637183</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -3268,19 +3268,19 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>0.2083333333333334</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="K62">
-        <v>0.198733331358149</v>
+        <v>0.146851692761069</v>
       </c>
       <c r="L62">
         <v>0.0736082159485815</v>
       </c>
       <c r="M62">
-        <v>0.1614917069393621</v>
+        <v>0.1123135487254382</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -3288,16 +3288,16 @@
         <v>74</v>
       </c>
       <c r="B63">
-        <v>0.1491954751155912</v>
+        <v>0.1128734585880629</v>
       </c>
       <c r="C63" t="s">
         <v>127</v>
       </c>
       <c r="D63">
-        <v>0.1835006396947929</v>
+        <v>0.1216576931116455</v>
       </c>
       <c r="E63">
-        <v>0.5105821077103836</v>
+        <v>0.4259637604473072</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>0.0736082159485815</v>
       </c>
       <c r="M63">
-        <v>0.1178201466620693</v>
+        <v>0.1048394425216523</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -3329,7 +3329,7 @@
         <v>75</v>
       </c>
       <c r="B64">
-        <v>0.1495369537871705</v>
+        <v>0.126398182335984</v>
       </c>
       <c r="C64" t="s">
         <v>127</v>
@@ -3338,7 +3338,7 @@
         <v>0.15</v>
       </c>
       <c r="E64">
-        <v>0.3634541318423091</v>
+        <v>0.07466324758506734</v>
       </c>
       <c r="F64">
         <v>0.15</v>
@@ -3362,7 +3362,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M64">
-        <v>0.1491134540839948</v>
+        <v>0.104812080348367</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -3370,7 +3370,7 @@
         <v>76</v>
       </c>
       <c r="B65">
-        <v>0.1123309848411256</v>
+        <v>0.0943416970650426</v>
       </c>
       <c r="C65" t="s">
         <v>127</v>
@@ -3388,22 +3388,22 @@
         <v>0.05273417468906039</v>
       </c>
       <c r="H65">
-        <v>0.2337640892848496</v>
+        <v>0.10010989966844</v>
       </c>
       <c r="I65">
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0.2416666666666666</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="K65">
-        <v>0.2564183618499601</v>
+        <v>0.183089795287125</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65">
-        <v>0.1292645178489815</v>
+        <v>0.0948223192781862</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -3452,19 +3452,19 @@
         <v>78</v>
       </c>
       <c r="B67">
-        <v>0.6250199960014442</v>
+        <v>0.3907341240311753</v>
       </c>
       <c r="C67" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D67">
-        <v>0.4789526571971764</v>
+        <v>0.1159620537350282</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0.8307633054738472</v>
       </c>
       <c r="F67">
-        <v>0.7369938687928519</v>
+        <v>0.3521239800572596</v>
       </c>
       <c r="G67">
         <v>0.535189241827146</v>
@@ -3473,19 +3473,19 @@
         <v>0.8142979598769708</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J67">
-        <v>0.7166666666666668</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K67">
-        <v>0.6727446725901431</v>
+        <v>0.5665208703755819</v>
       </c>
       <c r="L67">
         <v>0.82357389802428</v>
       </c>
       <c r="M67">
-        <v>0.7586124386418235</v>
+        <v>0.6420392572711584</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -3493,7 +3493,7 @@
         <v>79</v>
       </c>
       <c r="B68">
-        <v>0.1296221634421172</v>
+        <v>0.1189423410704612</v>
       </c>
       <c r="C68" t="s">
         <v>127</v>
@@ -3505,7 +3505,7 @@
         <v>0.07533675241493264</v>
       </c>
       <c r="F68">
-        <v>0.144017014604292</v>
+        <v>0.0740393739288</v>
       </c>
       <c r="G68">
         <v>0.09726582531093959</v>
@@ -3520,13 +3520,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K68">
-        <v>0.2022897775864878</v>
+        <v>0.1611659780921776</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
       <c r="M68">
-        <v>0.1109846981211264</v>
+        <v>0.0905371647110242</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -3534,7 +3534,7 @@
         <v>80</v>
       </c>
       <c r="B69">
-        <v>0.7925571198015806</v>
+        <v>0.7766696831301108</v>
       </c>
       <c r="C69" t="s">
         <v>130</v>
@@ -3546,7 +3546,7 @@
         <v>0.7019275208946145</v>
       </c>
       <c r="F69">
-        <v>0.7507046550935598</v>
+        <v>0.7092266914768259</v>
       </c>
       <c r="G69">
         <v>0.8505865050476622</v>
@@ -3561,13 +3561,13 @@
         <v>0.9166666666666665</v>
       </c>
       <c r="K69">
-        <v>0.657717052000202</v>
+        <v>0.5328769463924748</v>
       </c>
       <c r="L69">
         <v>0.9278522039514372</v>
       </c>
       <c r="M69">
-        <v>0.809966338681537</v>
+        <v>0.7795483335091919</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -3575,19 +3575,19 @@
         <v>81</v>
       </c>
       <c r="B70">
-        <v>0.2062297857612503</v>
+        <v>0.1357040382268071</v>
       </c>
       <c r="C70" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D70">
-        <v>0.1909794954748865</v>
+        <v>0.07457531793850132</v>
       </c>
       <c r="E70">
         <v>0.07533675241493264</v>
       </c>
       <c r="F70">
-        <v>0.1668959474028295</v>
+        <v>0.01262572425133065</v>
       </c>
       <c r="G70">
         <v>0.06378032426918739</v>
@@ -3608,7 +3608,7 @@
         <v>0.2391237480599879</v>
       </c>
       <c r="M70">
-        <v>0.2201776234298767</v>
+        <v>0.1916120538423874</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -3698,19 +3698,19 @@
         <v>84</v>
       </c>
       <c r="B73">
-        <v>0.6462567724523376</v>
+        <v>0.2161206510020912</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D73">
-        <v>0.6573256609068281</v>
+        <v>0.08516038517815186</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>0.4387214537529744</v>
+        <v>0.0251748746849241</v>
       </c>
       <c r="G73">
         <v>0.4224117033744367</v>
@@ -3719,19 +3719,19 @@
         <v>0.8389360490099596</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>0.7166666666666668</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="K73">
-        <v>0.5924653215646476</v>
+        <v>0.2067102764095038</v>
       </c>
       <c r="L73">
         <v>0.5828867762913704</v>
       </c>
       <c r="M73">
-        <v>0.6361332235600643</v>
+        <v>0.3358962417910585</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -3739,10 +3739,10 @@
         <v>85</v>
       </c>
       <c r="B74">
-        <v>0.1633981188544584</v>
+        <v>0.1164655533253321</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D74">
         <v>0.09421993680133545</v>
@@ -3751,13 +3751,13 @@
         <v>0.15</v>
       </c>
       <c r="F74">
-        <v>0.1317862184515397</v>
+        <v>0.0497190108178905</v>
       </c>
       <c r="G74">
-        <v>0.2636983207037986</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>0.6240331541224516</v>
+        <v>0.4235518696978371</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0.1499999999999999</v>
       </c>
       <c r="M74">
-        <v>0.2266681311210714</v>
+        <v>0.136811280671431</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -3862,13 +3862,13 @@
         <v>88</v>
       </c>
       <c r="B77">
-        <v>0.2110655966013123</v>
+        <v>0.1824689339023911</v>
       </c>
       <c r="C77" t="s">
         <v>128</v>
       </c>
       <c r="D77">
-        <v>0.1917943011483639</v>
+        <v>0.1418749951025147</v>
       </c>
       <c r="E77">
         <v>0.6173091736315381</v>
@@ -3889,13 +3889,13 @@
         <v>0.2416666666666666</v>
       </c>
       <c r="K77">
-        <v>0.2770361602103026</v>
+        <v>0.2271001179672117</v>
       </c>
       <c r="L77">
         <v>0.07639178405141835</v>
       </c>
       <c r="M77">
-        <v>0.228691025074776</v>
+        <v>0.2195959431644446</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -3903,7 +3903,7 @@
         <v>89</v>
       </c>
       <c r="B78">
-        <v>0.6934289354872627</v>
+        <v>0.6571649299064324</v>
       </c>
       <c r="C78" t="s">
         <v>129</v>
@@ -3912,10 +3912,10 @@
         <v>0.5057008628898092</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>0.9153816527369236</v>
       </c>
       <c r="F78">
-        <v>0.7319303345272333</v>
+        <v>0.4578745061115219</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3924,19 +3924,19 @@
         <v>0.8663458103835904</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J78">
-        <v>0.7166666666666668</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K78">
-        <v>0.6477766514685976</v>
+        <v>0.6164569126186727</v>
       </c>
       <c r="L78">
         <v>0.9999999999999989</v>
       </c>
       <c r="M78">
-        <v>0.8651240726463679</v>
+        <v>0.7956931926285407</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -3944,19 +3944,19 @@
         <v>90</v>
       </c>
       <c r="B79">
-        <v>0.4086870290058734</v>
+        <v>0.334377486284863</v>
       </c>
       <c r="C79" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D79">
-        <v>0.2598948678269162</v>
+        <v>0.2344301251162085</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>0.9153816527369236</v>
       </c>
       <c r="F79">
-        <v>0.577581470131755</v>
+        <v>0.3537436754376</v>
       </c>
       <c r="G79">
         <v>0.6052823722694305</v>
@@ -3965,19 +3965,19 @@
         <v>0.2560097569435651</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J79">
-        <v>0.7166666666666668</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K79">
-        <v>0.5924653215646476</v>
+        <v>0.2380300152594287</v>
       </c>
       <c r="L79">
         <v>0.2358762519400116</v>
       </c>
       <c r="M79">
-        <v>0.5447715802844725</v>
+        <v>0.4257888327452301</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -3985,13 +3985,13 @@
         <v>91</v>
       </c>
       <c r="B80">
-        <v>0.1335184156931837</v>
+        <v>0.1274362090162726</v>
       </c>
       <c r="C80" t="s">
         <v>127</v>
       </c>
       <c r="D80">
-        <v>0.1341123055854638</v>
+        <v>0.1213799342301099</v>
       </c>
       <c r="E80">
         <v>0.15</v>
@@ -4067,40 +4067,40 @@
         <v>93</v>
       </c>
       <c r="B82">
-        <v>0.8427830224139665</v>
+        <v>0.1486709210106874</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D82">
-        <v>0.7859352221962819</v>
+        <v>0</v>
       </c>
       <c r="E82">
-        <v>0.5769082636846183</v>
+        <v>0.07466324758506734</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>0.8115262876363287</v>
       </c>
       <c r="I82">
         <v>1</v>
       </c>
       <c r="J82">
-        <v>1</v>
+        <v>0.4333333333333336</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>0.4610101883533578</v>
       </c>
       <c r="L82">
-        <v>0.7453607198286045</v>
+        <v>0.3864431337300528</v>
       </c>
       <c r="M82">
-        <v>0.8947757303799099</v>
+        <v>0.2846445866501157</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -4149,13 +4149,13 @@
         <v>95</v>
       </c>
       <c r="B84">
-        <v>0.2468955359870152</v>
+        <v>0.162116073457696</v>
       </c>
       <c r="C84" t="s">
         <v>128</v>
       </c>
       <c r="D84">
-        <v>0.2504369298202226</v>
+        <v>0.1231192911221055</v>
       </c>
       <c r="E84">
         <v>0.4309413102863118</v>
@@ -4173,16 +4173,16 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <v>0.4083333333333332</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>0.2669224760432971</v>
+        <v>0.0150523783172804</v>
       </c>
       <c r="L84">
         <v>0</v>
       </c>
       <c r="M84">
-        <v>0.2436565952600694</v>
+        <v>0.197782331568332</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -4190,7 +4190,7 @@
         <v>96</v>
       </c>
       <c r="B85">
-        <v>0.09082669148904902</v>
+        <v>0.08845149401877586</v>
       </c>
       <c r="C85" t="s">
         <v>127</v>
@@ -4217,13 +4217,13 @@
         <v>0.2416666666666666</v>
       </c>
       <c r="K85">
-        <v>0.3540911250727201</v>
+        <v>0.3291231039511746</v>
       </c>
       <c r="L85">
         <v>0.02546392801713945</v>
       </c>
       <c r="M85">
-        <v>0.1293893179020817</v>
+        <v>0.124841776946916</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -4231,19 +4231,19 @@
         <v>97</v>
       </c>
       <c r="B86">
-        <v>0.6643241322757364</v>
+        <v>0.4415724015178892</v>
       </c>
       <c r="C86" t="s">
         <v>129</v>
       </c>
       <c r="D86">
-        <v>0.8377388220286279</v>
+        <v>0.5587955805379498</v>
       </c>
       <c r="E86">
-        <v>0.6798188022365362</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>0.3357552822116441</v>
+        <v>0.07031539117323786</v>
       </c>
       <c r="G86">
         <v>0.7319346119972763</v>
@@ -4258,13 +4258,13 @@
         <v>0.2666666666666666</v>
       </c>
       <c r="K86">
-        <v>0.4143772975621635</v>
+        <v>0.3159739202007785</v>
       </c>
       <c r="L86">
         <v>0.1499999999999999</v>
       </c>
       <c r="M86">
-        <v>0.5057199420203348</v>
+        <v>0.3343606802148462</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -4272,7 +4272,7 @@
         <v>98</v>
       </c>
       <c r="B87">
-        <v>0.07951837550270133</v>
+        <v>0.07672666440401182</v>
       </c>
       <c r="C87" t="s">
         <v>127</v>
@@ -4281,7 +4281,7 @@
         <v>0.07457531793850132</v>
       </c>
       <c r="E87">
-        <v>0.2545285466190942</v>
+        <v>0.2196856977460628</v>
       </c>
       <c r="F87">
         <v>0.07552462405477231</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>0.08403927072485889</v>
+        <v>0.07869427490233423</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -4313,19 +4313,19 @@
         <v>99</v>
       </c>
       <c r="B88">
-        <v>0.5073942250790531</v>
+        <v>0.3781599689108759</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D88">
-        <v>0.5811263962935378</v>
+        <v>0.467407194199117</v>
       </c>
       <c r="E88">
-        <v>0.6814368103037126</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>0.4188748484610289</v>
+        <v>0.208847793116929</v>
       </c>
       <c r="G88">
         <v>0.5771681432224739</v>
@@ -4346,7 +4346,7 @@
         <v>0.04999999999999995</v>
       </c>
       <c r="M88">
-        <v>0.4399591575659735</v>
+        <v>0.2965349121203979</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -4354,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="B89">
-        <v>0.01883765003950282</v>
+        <v>0.01324895010944833</v>
       </c>
       <c r="C89" t="s">
         <v>127</v>
@@ -4381,13 +4381,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K89">
-        <v>0.1057278932667589</v>
+        <v>0.04697960827488723</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89">
-        <v>0.03606646863086534</v>
+        <v>0.0253663722657696</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -4477,7 +4477,7 @@
         <v>103</v>
       </c>
       <c r="B92">
-        <v>0.2588690766028965</v>
+        <v>0.2386495114889209</v>
       </c>
       <c r="C92" t="s">
         <v>128</v>
@@ -4486,10 +4486,10 @@
         <v>0.1617206576515022</v>
       </c>
       <c r="E92">
-        <v>0.7865458681576908</v>
+        <v>0.7019275208946145</v>
       </c>
       <c r="F92">
-        <v>0.186831633463565</v>
+        <v>0.1562164156680373</v>
       </c>
       <c r="G92">
         <v>0.15</v>
@@ -4504,13 +4504,13 @@
         <v>0.2083333333333334</v>
       </c>
       <c r="K92">
-        <v>0.2035047598018518</v>
+        <v>0.09335172544209253</v>
       </c>
       <c r="L92">
         <v>0.3249999999999997</v>
       </c>
       <c r="M92">
-        <v>0.3477205247952865</v>
+        <v>0.3090082486152058</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -4518,7 +4518,7 @@
         <v>104</v>
       </c>
       <c r="B93">
-        <v>0.3312108778931498</v>
+        <v>0.2580680375751482</v>
       </c>
       <c r="C93" t="s">
         <v>128</v>
@@ -4536,22 +4536,22 @@
         <v>0.5</v>
       </c>
       <c r="H93">
-        <v>0.6663003344385335</v>
+        <v>0.3336996655614665</v>
       </c>
       <c r="I93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93">
-        <v>0.8583333333333334</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="K93">
-        <v>0.7425502549951863</v>
+        <v>0.2617809480474065</v>
       </c>
       <c r="L93">
         <v>0.4999999999999994</v>
       </c>
       <c r="M93">
-        <v>0.6341346565354251</v>
+        <v>0.4940957477347167</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -4559,40 +4559,40 @@
         <v>105</v>
       </c>
       <c r="B94">
-        <v>0.2911559635002317</v>
+        <v>0.1992386285611383</v>
       </c>
       <c r="C94" t="s">
         <v>128</v>
       </c>
       <c r="D94">
-        <v>0.2860286217459463</v>
+        <v>0.1732561897413833</v>
       </c>
       <c r="E94">
         <v>0.2818393167261321</v>
       </c>
       <c r="F94">
-        <v>0.2693436372418187</v>
+        <v>0.1162286086327428</v>
       </c>
       <c r="G94">
-        <v>0.1851652655455391</v>
+        <v>0.1265656387224728</v>
       </c>
       <c r="H94">
         <v>0.3086466968301532</v>
       </c>
       <c r="I94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94">
-        <v>0.4083333333333336</v>
+        <v>0.2416666666666666</v>
       </c>
       <c r="K94">
-        <v>0.3747419553706192</v>
+        <v>0.3121024776707694</v>
       </c>
       <c r="L94">
-        <v>0.3509621739585792</v>
+        <v>0.2024225938585991</v>
       </c>
       <c r="M94">
-        <v>0.295845404102178</v>
+        <v>0.2230020345086961</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -4600,7 +4600,7 @@
         <v>106</v>
       </c>
       <c r="B95">
-        <v>0.04740087803932961</v>
+        <v>0.04062100822822648</v>
       </c>
       <c r="C95" t="s">
         <v>127</v>
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0.3285182893742963</v>
+        <v>0.24389994211122</v>
       </c>
       <c r="F95">
         <v>0.03659820319123575</v>
@@ -4633,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="M95">
-        <v>0.09075347919172172</v>
+        <v>0.07777277505130466</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -4641,7 +4641,7 @@
         <v>107</v>
       </c>
       <c r="B96">
-        <v>0.07292055899263031</v>
+        <v>0.06614068918152717</v>
       </c>
       <c r="C96" t="s">
         <v>127</v>
@@ -4650,7 +4650,7 @@
         <v>0.04911057522779355</v>
       </c>
       <c r="E96">
-        <v>0.6173091736315381</v>
+        <v>0.5326908263684618</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -4674,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="M96">
-        <v>0.0946970486337175</v>
+        <v>0.08171634449330044</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -4682,7 +4682,7 @@
         <v>108</v>
       </c>
       <c r="B97">
-        <v>0.1151871393697446</v>
+        <v>0.08117211938339576</v>
       </c>
       <c r="C97" t="s">
         <v>127</v>
@@ -4694,7 +4694,7 @@
         <v>0.3136786334522643</v>
       </c>
       <c r="F97">
-        <v>0.2231366096092068</v>
+        <v>0</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -4709,13 +4709,13 @@
         <v>0.2416666666666666</v>
       </c>
       <c r="K97">
-        <v>0.2215421767716964</v>
+        <v>0.090827242664782</v>
       </c>
       <c r="L97">
         <v>0.3649829682456654</v>
       </c>
       <c r="M97">
-        <v>0.2205367091991934</v>
+        <v>0.1554117255232419</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -4764,19 +4764,19 @@
         <v>110</v>
       </c>
       <c r="B99">
-        <v>0.7531499652782216</v>
+        <v>0.6571131403027882</v>
       </c>
       <c r="C99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D99">
-        <v>0.7746637481777446</v>
+        <v>0.743742274886171</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>0.8307633054738472</v>
       </c>
       <c r="F99">
-        <v>0.9256487567822897</v>
+        <v>0.4220500554344596</v>
       </c>
       <c r="G99">
         <v>0.1337240281536406</v>
@@ -4791,13 +4791,13 @@
         <v>1</v>
       </c>
       <c r="K99">
-        <v>0.8221187420600257</v>
+        <v>0.6223745730876621</v>
       </c>
       <c r="L99">
         <v>0.9999999999999989</v>
       </c>
       <c r="M99">
-        <v>0.733473569230277</v>
+        <v>0.5778825759099899</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -4846,7 +4846,7 @@
         <v>112</v>
       </c>
       <c r="B101">
-        <v>0.3811457954842856</v>
+        <v>0.3787705980140124</v>
       </c>
       <c r="C101" t="s">
         <v>128</v>
@@ -4873,13 +4873,13 @@
         <v>0.2999999999999999</v>
       </c>
       <c r="K101">
-        <v>0.4310877200237737</v>
+        <v>0.4061196989022282</v>
       </c>
       <c r="L101">
         <v>0.2952920839800037</v>
       </c>
       <c r="M101">
-        <v>0.2689155800743886</v>
+        <v>0.264368039119223</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -4887,7 +4887,7 @@
         <v>113</v>
       </c>
       <c r="B102">
-        <v>0.1398013972337886</v>
+        <v>0.1338878960330976</v>
       </c>
       <c r="C102" t="s">
         <v>127</v>
@@ -4908,19 +4908,19 @@
         <v>0.3384200735311504</v>
       </c>
       <c r="I102">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J102">
-        <v>0.2083333333333335</v>
+        <v>0.125</v>
       </c>
       <c r="K102">
-        <v>0.2438904663099902</v>
+        <v>0.1817278778393327</v>
       </c>
       <c r="L102">
         <v>0.2546392801713945</v>
       </c>
       <c r="M102">
-        <v>0.2526909478657123</v>
+        <v>0.2413689886454244</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -4928,7 +4928,7 @@
         <v>114</v>
       </c>
       <c r="B103">
-        <v>0.08401381682046173</v>
+        <v>0.07255698196385003</v>
       </c>
       <c r="C103" t="s">
         <v>127</v>
@@ -4955,13 +4955,13 @@
         <v>0.2999999999999999</v>
       </c>
       <c r="K103">
-        <v>0.2331850440930662</v>
+        <v>0.1127510598597294</v>
       </c>
       <c r="L103">
         <v>0</v>
       </c>
       <c r="M103">
-        <v>0.1397804514473025</v>
+        <v>0.1178452538988563</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -4969,25 +4969,25 @@
         <v>115</v>
       </c>
       <c r="B104">
-        <v>0.249056651266472</v>
+        <v>0.1517725747934562</v>
       </c>
       <c r="C104" t="s">
         <v>128</v>
       </c>
       <c r="D104">
-        <v>0.1455074934907135</v>
+        <v>0.04991930604584918</v>
       </c>
       <c r="E104">
-        <v>0.59520045497346</v>
+        <v>0.5105821077103836</v>
       </c>
       <c r="F104">
-        <v>0.4949343762194697</v>
+        <v>0.3813632311904742</v>
       </c>
       <c r="G104">
         <v>0.0324219417703132</v>
       </c>
       <c r="H104">
-        <v>0.5655271329550725</v>
+        <v>0.2699387820561486</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4996,13 +4996,13 @@
         <v>0.2416666666666666</v>
       </c>
       <c r="K104">
-        <v>0.3640067678769851</v>
+        <v>0.2641346833908033</v>
       </c>
       <c r="L104">
         <v>0</v>
       </c>
       <c r="M104">
-        <v>0.3437621825225355</v>
+        <v>0.2449270545990555</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -5010,7 +5010,7 @@
         <v>116</v>
       </c>
       <c r="B105">
-        <v>0.2569364987512195</v>
+        <v>0.2470901566378799</v>
       </c>
       <c r="C105" t="s">
         <v>128</v>
@@ -5022,7 +5022,7 @@
         <v>0.05</v>
       </c>
       <c r="F105">
-        <v>0.6582174577346314</v>
+        <v>0.5809666087391273</v>
       </c>
       <c r="G105">
         <v>0.2812763789334853</v>
@@ -5037,13 +5037,13 @@
         <v>0.2416666666666666</v>
       </c>
       <c r="K105">
-        <v>0.3390387467554397</v>
+        <v>0.3140707256338942</v>
       </c>
       <c r="L105">
         <v>0.2523539580099978</v>
       </c>
       <c r="M105">
-        <v>0.2964164071766006</v>
+        <v>0.2775646508155453</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -5051,19 +5051,19 @@
         <v>117</v>
       </c>
       <c r="B106">
-        <v>0.5555021020244041</v>
+        <v>0.3511163912796449</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D106">
-        <v>0.4120586285318863</v>
+        <v>0.1842245067119203</v>
       </c>
       <c r="E106">
-        <v>0.8932729340788453</v>
+        <v>0.5547995450265401</v>
       </c>
       <c r="F106">
-        <v>0.9243688463848363</v>
+        <v>0.468643118615104</v>
       </c>
       <c r="G106">
         <v>0.6607598707337168</v>
@@ -5072,19 +5072,19 @@
         <v>0.5941289376163024</v>
       </c>
       <c r="I106">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J106">
-        <v>0.7166666666666668</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K106">
-        <v>0.7405996510918268</v>
+        <v>0.4845677221479929</v>
       </c>
       <c r="L106">
         <v>0.2655841679600076</v>
       </c>
       <c r="M106">
-        <v>0.6866947708411103</v>
+        <v>0.5037548572007281</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -5092,7 +5092,7 @@
         <v>118</v>
       </c>
       <c r="B107">
-        <v>0.2148046775650889</v>
+        <v>0.2000509200322302</v>
       </c>
       <c r="C107" t="s">
         <v>128</v>
@@ -5101,10 +5101,10 @@
         <v>0.2364416240455129</v>
       </c>
       <c r="E107">
-        <v>0.351525014472195</v>
+        <v>0.2818393167261321</v>
       </c>
       <c r="F107">
-        <v>0.1762621897365155</v>
+        <v>0.09155453743447106</v>
       </c>
       <c r="G107">
         <v>0.1265656387224728</v>
@@ -5119,13 +5119,13 @@
         <v>0.1833333333333333</v>
       </c>
       <c r="K107">
-        <v>0.246054069271184</v>
+        <v>0.2357731193976064</v>
       </c>
       <c r="L107">
         <v>0.2024225938585991</v>
       </c>
       <c r="M107">
-        <v>0.1950156367345967</v>
+        <v>0.1667681678554963</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -5133,7 +5133,7 @@
         <v>119</v>
       </c>
       <c r="B108">
-        <v>0.2717582867739882</v>
+        <v>0.2460470495950194</v>
       </c>
       <c r="C108" t="s">
         <v>128</v>
@@ -5142,10 +5142,10 @@
         <v>0.2235205846062349</v>
       </c>
       <c r="E108">
-        <v>0.716279659176744</v>
+        <v>0.6814368103037126</v>
       </c>
       <c r="F108">
-        <v>0.1371910616622555</v>
+        <v>0.03936242287996428</v>
       </c>
       <c r="G108">
         <v>0.192323654976707</v>
@@ -5154,19 +5154,19 @@
         <v>0.352918884966675</v>
       </c>
       <c r="I108">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J108">
-        <v>0.3833333333333334</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="K108">
-        <v>0.3696254001685633</v>
+        <v>0.2281526269588791</v>
       </c>
       <c r="L108">
         <v>0.1655155321114064</v>
       </c>
       <c r="M108">
-        <v>0.3158762430036459</v>
+        <v>0.2666496395137506</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -5215,7 +5215,7 @@
         <v>121</v>
       </c>
       <c r="B110">
-        <v>0.3830793960290095</v>
+        <v>0.3436749796527468</v>
       </c>
       <c r="C110" t="s">
         <v>128</v>
@@ -5227,7 +5227,7 @@
         <v>0.7019275208946145</v>
       </c>
       <c r="F110">
-        <v>0.5695921116466318</v>
+        <v>0.3674641240965996</v>
       </c>
       <c r="G110">
         <v>0.2231695591640398</v>
@@ -5245,10 +5245,10 @@
         <v>0.4391741411168048</v>
       </c>
       <c r="L110">
-        <v>0.4179724438943061</v>
+        <v>0.1778865218757386</v>
       </c>
       <c r="M110">
-        <v>0.4514164053715943</v>
+        <v>0.3759729108713883</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -5297,7 +5297,7 @@
         <v>123</v>
       </c>
       <c r="B112">
-        <v>0.01661042294170851</v>
+        <v>0.01090053627498748</v>
       </c>
       <c r="C112" t="s">
         <v>127</v>
@@ -5315,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>0.06929180601605563</v>
+        <v>0</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>0.03180223099570584</v>
+        <v>0.0208701111230444</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -5338,19 +5338,19 @@
         <v>124</v>
       </c>
       <c r="B113">
-        <v>0.8073270595573772</v>
+        <v>0.7080605644597759</v>
       </c>
       <c r="C113" t="s">
         <v>130</v>
       </c>
       <c r="D113">
-        <v>0.8460845882114489</v>
+        <v>0.6979978763983506</v>
       </c>
       <c r="E113">
         <v>1</v>
       </c>
       <c r="F113">
-        <v>0.8898758714035195</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="G113">
         <v>0.4726402015595599</v>
@@ -5359,19 +5359,19 @@
         <v>0.774131913621328</v>
       </c>
       <c r="I113">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J113">
-        <v>0.5250000000000002</v>
+        <v>0.4416666666666667</v>
       </c>
       <c r="K113">
-        <v>0.6182703812721432</v>
+        <v>0.4870785579360365</v>
       </c>
       <c r="L113">
         <v>0.8957216940728419</v>
       </c>
       <c r="M113">
-        <v>0.7718796216428676</v>
+        <v>0.7172638476075258</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -5379,7 +5379,7 @@
         <v>125</v>
       </c>
       <c r="B114">
-        <v>0.4935003757729489</v>
+        <v>0.4407467228894335</v>
       </c>
       <c r="C114" t="s">
         <v>129</v>
@@ -5388,10 +5388,10 @@
         <v>0.4331568546537495</v>
       </c>
       <c r="E114">
-        <v>0.9153816527369236</v>
+        <v>0.4480724791053855</v>
       </c>
       <c r="F114">
-        <v>0.3773083518179365</v>
+        <v>0.2392146296411173</v>
       </c>
       <c r="G114">
         <v>0.6738474634857513</v>
@@ -5406,13 +5406,13 @@
         <v>0.3250000000000001</v>
       </c>
       <c r="K114">
-        <v>0.3404214248103664</v>
+        <v>0.3198595250632113</v>
       </c>
       <c r="L114">
         <v>0.3382302099500095</v>
       </c>
       <c r="M114">
-        <v>0.548690252235596</v>
+        <v>0.4476883776441789</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -5420,13 +5420,13 @@
         <v>126</v>
       </c>
       <c r="B115">
-        <v>0.1508759096135642</v>
+        <v>0.06697490117631651</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D115">
-        <v>0.1428830140459937</v>
+        <v>0.0577226288678418</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0.1249999999999999</v>
       </c>
       <c r="K115">
-        <v>0.2951911123655449</v>
+        <v>0.09544694339318134</v>
       </c>
       <c r="L115">
-        <v>0.3664433881456851</v>
+        <v>0.0736082159485815</v>
       </c>
       <c r="M115">
-        <v>0.158186171109271</v>
+        <v>0.07543698221223774</v>
       </c>
     </row>
   </sheetData>
